--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507128</v>
+        <v>122507172</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509949</v>
+        <v>510070</v>
       </c>
       <c r="R2" t="n">
-        <v>7107180</v>
+        <v>7106961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507172</v>
+        <v>122507133</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510070</v>
+        <v>509814</v>
       </c>
       <c r="R3" t="n">
-        <v>7106961</v>
+        <v>7107345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507125</v>
+        <v>122507132</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -902,11 +892,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509687</v>
+        <v>509824</v>
       </c>
       <c r="R4" t="n">
-        <v>7107334</v>
+        <v>7107304</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507133</v>
+        <v>122507125</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1009,11 +994,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1031,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509814</v>
+        <v>509687</v>
       </c>
       <c r="R5" t="n">
-        <v>7107345</v>
+        <v>7107334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507132</v>
+        <v>122507171</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1094,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509824</v>
+        <v>510063</v>
       </c>
       <c r="R6" t="n">
-        <v>7107304</v>
+        <v>7106959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507129</v>
+        <v>122507127</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1223,11 +1193,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1245,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509936</v>
+        <v>510041</v>
       </c>
       <c r="R7" t="n">
-        <v>7107192</v>
+        <v>7106986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,11 +1295,6 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1419,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507126</v>
+        <v>122507128</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1437,11 +1397,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1459,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509792</v>
+        <v>509949</v>
       </c>
       <c r="R9" t="n">
-        <v>7107237</v>
+        <v>7107180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507127</v>
+        <v>122507126</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1544,11 +1499,6 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1566,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510041</v>
+        <v>509792</v>
       </c>
       <c r="R10" t="n">
-        <v>7106986</v>
+        <v>7107237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507171</v>
+        <v>122507129</v>
       </c>
       <c r="B11" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1599,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510063</v>
+        <v>509936</v>
       </c>
       <c r="R11" t="n">
-        <v>7106959</v>
+        <v>7107192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507172</v>
+        <v>122507128</v>
       </c>
       <c r="B2" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510070</v>
+        <v>509949</v>
       </c>
       <c r="R2" t="n">
-        <v>7106961</v>
+        <v>7107180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507133</v>
+        <v>122507129</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,6 +800,11 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509814</v>
+        <v>509936</v>
       </c>
       <c r="R3" t="n">
-        <v>7107345</v>
+        <v>7107192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507132</v>
+        <v>122507127</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -892,6 +907,11 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -909,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509824</v>
+        <v>510041</v>
       </c>
       <c r="R4" t="n">
-        <v>7107304</v>
+        <v>7106986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507125</v>
+        <v>122507171</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -992,16 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509687</v>
+        <v>510063</v>
       </c>
       <c r="R5" t="n">
-        <v>7107334</v>
+        <v>7106959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507171</v>
+        <v>122507132</v>
       </c>
       <c r="B6" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1094,16 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510063</v>
+        <v>509824</v>
       </c>
       <c r="R6" t="n">
-        <v>7106959</v>
+        <v>7107304</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507127</v>
+        <v>122507133</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1193,6 +1223,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1210,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510041</v>
+        <v>509814</v>
       </c>
       <c r="R7" t="n">
-        <v>7106986</v>
+        <v>7107345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1315,7 @@
         <v>122507131</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1294,6 +1329,11 @@
       </c>
       <c r="E8" t="n">
         <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1379,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507128</v>
+        <v>122507126</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1397,6 +1437,11 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1414,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509949</v>
+        <v>509792</v>
       </c>
       <c r="R9" t="n">
-        <v>7107180</v>
+        <v>7107237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507126</v>
+        <v>122507172</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1497,16 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509792</v>
+        <v>510070</v>
       </c>
       <c r="R10" t="n">
-        <v>7107237</v>
+        <v>7106961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507129</v>
+        <v>122507125</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1601,6 +1646,11 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1618,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509936</v>
+        <v>509687</v>
       </c>
       <c r="R11" t="n">
-        <v>7107192</v>
+        <v>7107334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507128</v>
+        <v>122507129</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509949</v>
+        <v>509936</v>
       </c>
       <c r="R2" t="n">
-        <v>7107180</v>
+        <v>7107192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507129</v>
+        <v>122507133</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509936</v>
+        <v>509814</v>
       </c>
       <c r="R3" t="n">
-        <v>7107192</v>
+        <v>7107345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507171</v>
+        <v>122507128</v>
       </c>
       <c r="B5" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510063</v>
+        <v>509949</v>
       </c>
       <c r="R5" t="n">
-        <v>7106959</v>
+        <v>7107180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507133</v>
+        <v>122507125</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509814</v>
+        <v>509687</v>
       </c>
       <c r="R7" t="n">
-        <v>7107345</v>
+        <v>7107334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507126</v>
+        <v>122507172</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509792</v>
+        <v>510070</v>
       </c>
       <c r="R9" t="n">
-        <v>7107237</v>
+        <v>7106961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1500,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507172</v>
+        <v>122507126</v>
       </c>
       <c r="B10" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510070</v>
+        <v>509792</v>
       </c>
       <c r="R10" t="n">
-        <v>7106961</v>
+        <v>7107237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507125</v>
+        <v>122507171</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509687</v>
+        <v>510063</v>
       </c>
       <c r="R11" t="n">
-        <v>7107334</v>
+        <v>7106959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507129</v>
+        <v>122507131</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509936</v>
+        <v>509926</v>
       </c>
       <c r="R2" t="n">
-        <v>7107192</v>
+        <v>7107211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507133</v>
+        <v>122507172</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509814</v>
+        <v>510070</v>
       </c>
       <c r="R3" t="n">
-        <v>7107345</v>
+        <v>7106961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507127</v>
+        <v>122507125</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510041</v>
+        <v>509687</v>
       </c>
       <c r="R4" t="n">
-        <v>7106986</v>
+        <v>7107334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507128</v>
+        <v>122507129</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509949</v>
+        <v>509936</v>
       </c>
       <c r="R5" t="n">
-        <v>7107180</v>
+        <v>7107192</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507132</v>
+        <v>122507128</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509824</v>
+        <v>509949</v>
       </c>
       <c r="R6" t="n">
-        <v>7107304</v>
+        <v>7107180</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507125</v>
+        <v>122507132</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509687</v>
+        <v>509824</v>
       </c>
       <c r="R7" t="n">
-        <v>7107334</v>
+        <v>7107304</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507131</v>
+        <v>122507127</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509926</v>
+        <v>510041</v>
       </c>
       <c r="R8" t="n">
-        <v>7107211</v>
+        <v>7106986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507172</v>
+        <v>122507171</v>
       </c>
       <c r="B9" t="n">
         <v>90857</v>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510070</v>
+        <v>510063</v>
       </c>
       <c r="R9" t="n">
-        <v>7106961</v>
+        <v>7106959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507126</v>
+        <v>122507133</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509792</v>
+        <v>509814</v>
       </c>
       <c r="R10" t="n">
-        <v>7107237</v>
+        <v>7107345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507171</v>
+        <v>122507126</v>
       </c>
       <c r="B11" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510063</v>
+        <v>509792</v>
       </c>
       <c r="R11" t="n">
-        <v>7106959</v>
+        <v>7107237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507131</v>
+        <v>122507127</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509926</v>
+        <v>510041</v>
       </c>
       <c r="R2" t="n">
-        <v>7107211</v>
+        <v>7106986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507172</v>
+        <v>122507133</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510070</v>
+        <v>509814</v>
       </c>
       <c r="R3" t="n">
-        <v>7106961</v>
+        <v>7107345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507125</v>
+        <v>122507126</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509687</v>
+        <v>509792</v>
       </c>
       <c r="R4" t="n">
-        <v>7107334</v>
+        <v>7107237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507129</v>
+        <v>122507125</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509936</v>
+        <v>509687</v>
       </c>
       <c r="R5" t="n">
-        <v>7107192</v>
+        <v>7107334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507128</v>
+        <v>122507132</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509949</v>
+        <v>509824</v>
       </c>
       <c r="R6" t="n">
-        <v>7107180</v>
+        <v>7107304</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507132</v>
+        <v>122507171</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509824</v>
+        <v>510063</v>
       </c>
       <c r="R7" t="n">
-        <v>7107304</v>
+        <v>7106959</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507127</v>
+        <v>122507131</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510041</v>
+        <v>509926</v>
       </c>
       <c r="R8" t="n">
-        <v>7106986</v>
+        <v>7107211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507171</v>
+        <v>122507172</v>
       </c>
       <c r="B9" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510063</v>
+        <v>510070</v>
       </c>
       <c r="R9" t="n">
-        <v>7106959</v>
+        <v>7106961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507133</v>
+        <v>122507129</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509814</v>
+        <v>509936</v>
       </c>
       <c r="R10" t="n">
-        <v>7107345</v>
+        <v>7107192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507126</v>
+        <v>122507128</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509792</v>
+        <v>509949</v>
       </c>
       <c r="R11" t="n">
-        <v>7107237</v>
+        <v>7107180</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507127</v>
+        <v>122507126</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510041</v>
+        <v>509792</v>
       </c>
       <c r="R2" t="n">
-        <v>7106986</v>
+        <v>7107237</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507133</v>
+        <v>122507127</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509814</v>
+        <v>510041</v>
       </c>
       <c r="R3" t="n">
-        <v>7107345</v>
+        <v>7106986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507126</v>
+        <v>122507171</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509792</v>
+        <v>510063</v>
       </c>
       <c r="R4" t="n">
-        <v>7107237</v>
+        <v>7106959</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507125</v>
+        <v>122507172</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509687</v>
+        <v>510070</v>
       </c>
       <c r="R5" t="n">
-        <v>7107334</v>
+        <v>7106961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507171</v>
+        <v>122507131</v>
       </c>
       <c r="B7" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510063</v>
+        <v>509926</v>
       </c>
       <c r="R7" t="n">
-        <v>7106959</v>
+        <v>7107211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507131</v>
+        <v>122507128</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509926</v>
+        <v>509949</v>
       </c>
       <c r="R8" t="n">
-        <v>7107211</v>
+        <v>7107180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507172</v>
+        <v>122507125</v>
       </c>
       <c r="B9" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510070</v>
+        <v>509687</v>
       </c>
       <c r="R9" t="n">
-        <v>7106961</v>
+        <v>7107334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507128</v>
+        <v>122507133</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509949</v>
+        <v>509814</v>
       </c>
       <c r="R11" t="n">
-        <v>7107180</v>
+        <v>7107345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122507126</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507127</v>
+        <v>122507172</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510041</v>
+        <v>510070</v>
       </c>
       <c r="R3" t="n">
-        <v>7106986</v>
+        <v>7106961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507171</v>
+        <v>122507128</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510063</v>
+        <v>509949</v>
       </c>
       <c r="R4" t="n">
-        <v>7106959</v>
+        <v>7107180</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507172</v>
+        <v>122507133</v>
       </c>
       <c r="B5" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510070</v>
+        <v>509814</v>
       </c>
       <c r="R5" t="n">
-        <v>7106961</v>
+        <v>7107345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507132</v>
+        <v>122507129</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509824</v>
+        <v>509936</v>
       </c>
       <c r="R6" t="n">
-        <v>7107304</v>
+        <v>7107192</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507131</v>
+        <v>122507127</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509926</v>
+        <v>510041</v>
       </c>
       <c r="R7" t="n">
-        <v>7107211</v>
+        <v>7106986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507128</v>
+        <v>122507125</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509949</v>
+        <v>509687</v>
       </c>
       <c r="R8" t="n">
-        <v>7107180</v>
+        <v>7107334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507125</v>
+        <v>122507131</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509687</v>
+        <v>509926</v>
       </c>
       <c r="R9" t="n">
-        <v>7107334</v>
+        <v>7107211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507129</v>
+        <v>122507171</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509936</v>
+        <v>510063</v>
       </c>
       <c r="R10" t="n">
-        <v>7107192</v>
+        <v>7106959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507133</v>
+        <v>122507132</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509814</v>
+        <v>509824</v>
       </c>
       <c r="R11" t="n">
-        <v>7107345</v>
+        <v>7107304</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507126</v>
+        <v>122507131</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509792</v>
+        <v>509926</v>
       </c>
       <c r="R2" t="n">
-        <v>7107237</v>
+        <v>7107211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507172</v>
+        <v>122507127</v>
       </c>
       <c r="B3" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510070</v>
+        <v>510041</v>
       </c>
       <c r="R3" t="n">
-        <v>7106961</v>
+        <v>7106986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507133</v>
+        <v>122507126</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509814</v>
+        <v>509792</v>
       </c>
       <c r="R5" t="n">
-        <v>7107345</v>
+        <v>7107237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507129</v>
+        <v>122507125</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509936</v>
+        <v>509687</v>
       </c>
       <c r="R6" t="n">
-        <v>7107192</v>
+        <v>7107334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507127</v>
+        <v>122507171</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510041</v>
+        <v>510063</v>
       </c>
       <c r="R7" t="n">
-        <v>7106986</v>
+        <v>7106959</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507125</v>
+        <v>122507132</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509687</v>
+        <v>509824</v>
       </c>
       <c r="R8" t="n">
-        <v>7107334</v>
+        <v>7107304</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507131</v>
+        <v>122507172</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509926</v>
+        <v>510070</v>
       </c>
       <c r="R9" t="n">
-        <v>7107211</v>
+        <v>7106961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507171</v>
+        <v>122507129</v>
       </c>
       <c r="B10" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510063</v>
+        <v>509936</v>
       </c>
       <c r="R10" t="n">
-        <v>7106959</v>
+        <v>7107192</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507132</v>
+        <v>122507133</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509824</v>
+        <v>509814</v>
       </c>
       <c r="R11" t="n">
-        <v>7107304</v>
+        <v>7107345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507127</v>
+        <v>122507171</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510041</v>
+        <v>510063</v>
       </c>
       <c r="R3" t="n">
-        <v>7106986</v>
+        <v>7106959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507128</v>
+        <v>122507127</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509949</v>
+        <v>510041</v>
       </c>
       <c r="R4" t="n">
-        <v>7107180</v>
+        <v>7106986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507126</v>
+        <v>122507125</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509792</v>
+        <v>509687</v>
       </c>
       <c r="R5" t="n">
-        <v>7107237</v>
+        <v>7107334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507125</v>
+        <v>122507128</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509687</v>
+        <v>509949</v>
       </c>
       <c r="R6" t="n">
-        <v>7107334</v>
+        <v>7107180</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507171</v>
+        <v>122507129</v>
       </c>
       <c r="B7" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510063</v>
+        <v>509936</v>
       </c>
       <c r="R7" t="n">
-        <v>7106959</v>
+        <v>7107192</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507132</v>
+        <v>122507133</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509824</v>
+        <v>509814</v>
       </c>
       <c r="R8" t="n">
-        <v>7107304</v>
+        <v>7107345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507172</v>
+        <v>122507126</v>
       </c>
       <c r="B9" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510070</v>
+        <v>509792</v>
       </c>
       <c r="R9" t="n">
-        <v>7106961</v>
+        <v>7107237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507129</v>
+        <v>122507172</v>
       </c>
       <c r="B10" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509936</v>
+        <v>510070</v>
       </c>
       <c r="R10" t="n">
-        <v>7107192</v>
+        <v>7106961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507133</v>
+        <v>122507132</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509814</v>
+        <v>509824</v>
       </c>
       <c r="R11" t="n">
-        <v>7107345</v>
+        <v>7107304</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507131</v>
+        <v>122507132</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509926</v>
+        <v>509824</v>
       </c>
       <c r="R2" t="n">
-        <v>7107211</v>
+        <v>7107304</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507127</v>
+        <v>122507133</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510041</v>
+        <v>509814</v>
       </c>
       <c r="R3" t="n">
-        <v>7106986</v>
+        <v>7107345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507133</v>
+        <v>122507127</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509814</v>
+        <v>510041</v>
       </c>
       <c r="R4" t="n">
-        <v>7107345</v>
+        <v>7106986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507172</v>
+        <v>122507131</v>
       </c>
       <c r="B5" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510070</v>
+        <v>509926</v>
       </c>
       <c r="R5" t="n">
-        <v>7106961</v>
+        <v>7107211</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507125</v>
+        <v>122507126</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509687</v>
+        <v>509792</v>
       </c>
       <c r="R6" t="n">
-        <v>7107334</v>
+        <v>7107237</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507126</v>
+        <v>122507172</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509792</v>
+        <v>510070</v>
       </c>
       <c r="R7" t="n">
-        <v>7107237</v>
+        <v>7106961</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,7 +1315,7 @@
         <v>122507171</v>
       </c>
       <c r="B8" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507132</v>
+        <v>122507128</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509824</v>
+        <v>509949</v>
       </c>
       <c r="R9" t="n">
-        <v>7107304</v>
+        <v>7107180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507129</v>
+        <v>122507125</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509936</v>
+        <v>509687</v>
       </c>
       <c r="R10" t="n">
-        <v>7107192</v>
+        <v>7107334</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507128</v>
+        <v>122507129</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509949</v>
+        <v>509936</v>
       </c>
       <c r="R11" t="n">
-        <v>7107180</v>
+        <v>7107192</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507132</v>
+        <v>122507129</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509824</v>
+        <v>509936</v>
       </c>
       <c r="R2" t="n">
-        <v>7107304</v>
+        <v>7107192</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507133</v>
+        <v>122507171</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509814</v>
+        <v>510063</v>
       </c>
       <c r="R3" t="n">
-        <v>7107345</v>
+        <v>7106959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507127</v>
+        <v>122507132</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510041</v>
+        <v>509824</v>
       </c>
       <c r="R4" t="n">
-        <v>7106986</v>
+        <v>7107304</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507126</v>
+        <v>122507125</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509792</v>
+        <v>509687</v>
       </c>
       <c r="R6" t="n">
-        <v>7107237</v>
+        <v>7107334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507172</v>
+        <v>122507133</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510070</v>
+        <v>509814</v>
       </c>
       <c r="R7" t="n">
-        <v>7106961</v>
+        <v>7107345</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507171</v>
+        <v>122507127</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510063</v>
+        <v>510041</v>
       </c>
       <c r="R8" t="n">
-        <v>7106959</v>
+        <v>7106986</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1388,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507128</v>
+        <v>122507172</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509949</v>
+        <v>510070</v>
       </c>
       <c r="R9" t="n">
-        <v>7107180</v>
+        <v>7106961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507125</v>
+        <v>122507128</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509687</v>
+        <v>509949</v>
       </c>
       <c r="R10" t="n">
-        <v>7107334</v>
+        <v>7107180</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507129</v>
+        <v>122507126</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509936</v>
+        <v>509792</v>
       </c>
       <c r="R11" t="n">
-        <v>7107192</v>
+        <v>7107237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 55040-2024 artfynd.xlsx
+++ b/artfynd/A 55040-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507171</v>
+        <v>122507128</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510063</v>
+        <v>509949</v>
       </c>
       <c r="R3" t="n">
-        <v>7106959</v>
+        <v>7107180</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507132</v>
+        <v>122507126</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509824</v>
+        <v>509792</v>
       </c>
       <c r="R4" t="n">
-        <v>7107304</v>
+        <v>7107237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507131</v>
+        <v>122507125</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509926</v>
+        <v>509687</v>
       </c>
       <c r="R5" t="n">
-        <v>7107211</v>
+        <v>7107334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507125</v>
+        <v>122507131</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509687</v>
+        <v>509926</v>
       </c>
       <c r="R6" t="n">
-        <v>7107334</v>
+        <v>7107211</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507133</v>
+        <v>122507132</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509814</v>
+        <v>509824</v>
       </c>
       <c r="R7" t="n">
-        <v>7107345</v>
+        <v>7107304</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507128</v>
+        <v>122507171</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509949</v>
+        <v>510063</v>
       </c>
       <c r="R10" t="n">
-        <v>7107180</v>
+        <v>7106959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507126</v>
+        <v>122507133</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509792</v>
+        <v>509814</v>
       </c>
       <c r="R11" t="n">
-        <v>7107237</v>
+        <v>7107345</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
